--- a/mock-data/out/차원테이블_20260828.xlsx
+++ b/mock-data/out/차원테이블_20260828.xlsx
@@ -10,6 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DIM_Service" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DIM_Department" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DIM_OS" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DIM_TACS_Scope_Rule" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -18,7 +19,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
+  </numFmts>
   <fonts count="1">
     <font>
       <name val="Calibri"/>
@@ -48,8 +51,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -1190,4 +1194,475 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G13"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>RuleKey</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>적용조건_서비스등급</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>적용조건_OS계열</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>적용조건_서비스구분</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>대상여부</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>규칙설명</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>최종개정일</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>RULE001</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>ALL</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>운영</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>운영환경 Critical등급 기본 원칙</t>
+        </is>
+      </c>
+      <c r="G2" s="1" t="n">
+        <v>46150</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>RULE002</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>ALL</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>개발</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>개발환경 Critical등급 기본 원칙</t>
+        </is>
+      </c>
+      <c r="G3" s="1" t="n">
+        <v>46115</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>RULE003</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>ALL</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>운영</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>운영환경 High등급 기본 원칙</t>
+        </is>
+      </c>
+      <c r="G4" s="1" t="n">
+        <v>46007</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>RULE004</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>ALL</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>개발</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>개발환경 High등급 기본 원칙</t>
+        </is>
+      </c>
+      <c r="G5" s="1" t="n">
+        <v>46117</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>RULE005</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>ALL</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>운영</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>운영환경 Medium등급 기본 원칙</t>
+        </is>
+      </c>
+      <c r="G6" s="1" t="n">
+        <v>45969</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>RULE006</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>ALL</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>개발</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>개발환경 Medium등급 기본 원칙</t>
+        </is>
+      </c>
+      <c r="G7" s="1" t="n">
+        <v>46161</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>RULE007</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>ALL</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>운영</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>운영환경 Low등급 기본 원칙</t>
+        </is>
+      </c>
+      <c r="G8" s="1" t="n">
+        <v>45953</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>RULE008</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>ALL</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>개발</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>개발환경 Low등급 기본 원칙</t>
+        </is>
+      </c>
+      <c r="G9" s="1" t="n">
+        <v>46035</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>RULE009</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>ALL</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>RHEL 7.9 (EOS)</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>ALL</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>RHEL 7.9는 EOS 대상으로 TACS 적용 제외</t>
+        </is>
+      </c>
+      <c r="G10" s="1" t="n">
+        <v>46225</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>RULE010</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>ALL</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Windows2012 R2 (EOS)</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>ALL</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Windows2012 R2는 EOS 대상으로 TACS 적용 제외</t>
+        </is>
+      </c>
+      <c r="G11" s="1" t="n">
+        <v>46033</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>RULE011</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>ALL</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>폐기예정 장비</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>ALL</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>설비상태=폐기예정 장비는 TACS 적용 제외</t>
+        </is>
+      </c>
+      <c r="G12" s="1" t="n">
+        <v>46247</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>RULE012</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>ALL</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>장기 미접속 장비</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>ALL</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>미접속일수 90일 이상 장비는 TACS 적용 제외 검토 대상</t>
+        </is>
+      </c>
+      <c r="G13" s="1" t="n">
+        <v>46039</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>